--- a/Rstudio/Dynamic chambers/N-NH3 extrapolated cattle.xlsx
+++ b/Rstudio/Dynamic chambers/N-NH3 extrapolated cattle.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lorenzobenedetti/Desktop/Università/DiANA/Dottorato/Danimarca/AU/Agroscena Next/DFC_SC_Lorenzo_Pablo/DFC NH3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lorenzobenedetti/Documents/GitHub/Benedetti-2026-N2O-AgroscenaNext/Rstudio/Dynamic chambers/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8B42A0B-244C-D24C-A6DA-990A0348DA73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE84E308-4BFE-5144-AD81-AF9220C2880F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1400" windowWidth="27640" windowHeight="16600" xr2:uid="{911B98E2-1653-974C-B550-808959C14137}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="7">
   <si>
     <t>VALVE_ID</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>CSRAW</t>
+  </si>
+  <si>
+    <t>BLOCK</t>
   </si>
 </sst>
 </file>
@@ -452,119 +455,149 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D442E20-864E-6040-98E1-194B745C59A2}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>4</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="4">
+      <c r="D2" s="4">
         <v>10.556448937106699</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>14</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4">
+      <c r="D3" s="4">
         <v>12.0422199993014</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>17</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3">
         <v>3</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="4">
         <v>7.9086948567529198</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>8</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="4">
+      <c r="D5" s="4">
         <v>7.3520284333197496</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>12</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3">
+        <v>2</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="4">
+      <c r="D6" s="4">
         <v>11.993285655982699</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>18</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3">
+        <v>3</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="4">
+      <c r="D7" s="4">
         <v>11.4312601848988</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>11</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="4">
+      <c r="D8" s="4">
         <v>16.090073506373201</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>13</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3">
+        <v>2</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="4">
+      <c r="D9" s="4">
         <v>18.780529033220901</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>15</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3">
+        <v>3</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="4">
+      <c r="D10" s="4">
         <v>17.183244649245101</v>
       </c>
     </row>
